--- a/artfynd/A 51106-2020 artfynd.xlsx
+++ b/artfynd/A 51106-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51106-2020 artfynd.xlsx
+++ b/artfynd/A 51106-2020 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74658489</v>
       </c>
       <c r="B2" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480743.2812889343</v>
+        <v>480743</v>
       </c>
       <c r="R2" t="n">
-        <v>6414200.208838279</v>
+        <v>6414200</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1988-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 51106-2020 artfynd.xlsx
+++ b/artfynd/A 51106-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74658489</v>
       </c>
       <c r="B2" t="n">
-        <v>105627</v>
+        <v>105636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51106-2020 artfynd.xlsx
+++ b/artfynd/A 51106-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74658489</v>
       </c>
       <c r="B2" t="n">
-        <v>105636</v>
+        <v>105639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51106-2020 artfynd.xlsx
+++ b/artfynd/A 51106-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74658489</v>
       </c>
       <c r="B2" t="n">
-        <v>105639</v>
+        <v>105667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51106-2020 artfynd.xlsx
+++ b/artfynd/A 51106-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74658489</v>
       </c>
       <c r="B2" t="n">
-        <v>105667</v>
+        <v>105673</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51106-2020 artfynd.xlsx
+++ b/artfynd/A 51106-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74658489</v>
       </c>
       <c r="B2" t="n">
-        <v>105673</v>
+        <v>105680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51106-2020 artfynd.xlsx
+++ b/artfynd/A 51106-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74658489</v>
       </c>
       <c r="B2" t="n">
-        <v>105680</v>
+        <v>105684</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
